--- a/# четверть_#_полезные ссылки для тестирования сайтов рассылок.xlsx
+++ b/# четверть_#_полезные ссылки для тестирования сайтов рассылок.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{870A7E86-91FB-4CCE-A221-8210C58E4391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D74E34B0-8FDE-4F8C-8E64-52E46D85CE96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8940" yWindow="-17025" windowWidth="23250" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-13875" yWindow="-21720" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="12" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -152,18 +152,46 @@
   </si>
   <si>
     <t>Запуск нейронок на локально арендованном сервере</t>
+  </si>
+  <si>
+    <t>dBeaver -&gt; Microsoft SQL Management Studio -&gt; dataGrip (позволяет более удобно менять значения в бд)</t>
+  </si>
+  <si>
+    <t>datagrip</t>
+  </si>
+  <si>
+    <t>`https://habr.com/ru/articles/774908/</t>
+  </si>
+  <si>
+    <t>Fooocus - ИИ для генерации изображений</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="20" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -332,9 +360,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -345,23 +373,29 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -687,7 +721,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:V22"/>
+  <dimension ref="A2:V24"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -902,8 +936,24 @@
         <v>39</v>
       </c>
     </row>
+    <row r="23" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="C4" r:id="rId1" xr:uid="{E8D62272-8175-47AE-9712-C94739EB9ACC}"/>
     <hyperlink ref="D5" r:id="rId2" xr:uid="{14C24C52-D807-4F34-9DBD-8A3F76FDA123}"/>

--- a/# четверть_#_полезные ссылки для тестирования сайтов рассылок.xlsx
+++ b/# четверть_#_полезные ссылки для тестирования сайтов рассылок.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D74E34B0-8FDE-4F8C-8E64-52E46D85CE96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5131EE9B-90BB-477E-82D7-A0511830B4C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-13875" yWindow="-21720" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -164,18 +164,97 @@
   </si>
   <si>
     <t>Fooocus - ИИ для генерации изображений</t>
+  </si>
+  <si>
+    <t>свой почтовый сервер</t>
+  </si>
+  <si>
+    <t>https://here.now/</t>
+  </si>
+  <si>
+    <t>свое хранилище паролей</t>
+  </si>
+  <si>
+    <t>https://vault.hwcompany.ru/#/login</t>
+  </si>
+  <si>
+    <t>можно выкладывать свой сайтик и ограничивать к нему доступ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://github.com/dani-garcia/vaultwarden</t>
+  </si>
+  <si>
+    <t>https://github.com/heygen-com/hyperframes</t>
+  </si>
+  <si>
+    <t>создает видео презентации</t>
+  </si>
+  <si>
+    <t>vespa полнотекстовый поиск</t>
+  </si>
+  <si>
+    <t>`https://habr.com/ru/companies/sportmaster_lab/articles/827460/</t>
+  </si>
+  <si>
+    <t>https://mailu.io/2024.06/</t>
+  </si>
+  <si>
+    <t>rancher</t>
+  </si>
+  <si>
+    <t>возможность администрирования kubernetes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="25" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -360,9 +439,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -373,25 +452,40 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -421,6 +515,9 @@
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -721,7 +818,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:V24"/>
+  <dimension ref="A2:V30"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -952,13 +1049,67 @@
         <v>43</v>
       </c>
     </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="30" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="31" t="s">
+        <v>56</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="23" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="C4" r:id="rId1" xr:uid="{E8D62272-8175-47AE-9712-C94739EB9ACC}"/>
     <hyperlink ref="D5" r:id="rId2" xr:uid="{14C24C52-D807-4F34-9DBD-8A3F76FDA123}"/>
+    <hyperlink ref="A25" r:id="rId3" xr:uid="{61EBBDB6-449F-431B-AC83-3C57763031B0}"/>
+    <hyperlink ref="A26" r:id="rId4" location="/login" xr:uid="{B46E902B-C529-4206-BD22-BEEA9822369B}"/>
+    <hyperlink ref="A27" r:id="rId5" xr:uid="{D6D2D2A3-BEEF-453F-A91F-AAB01E05A8F8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId6"/>
 </worksheet>
 </file>
--- a/# четверть_#_полезные ссылки для тестирования сайтов рассылок.xlsx
+++ b/# четверть_#_полезные ссылки для тестирования сайтов рассылок.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5131EE9B-90BB-477E-82D7-A0511830B4C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF5DB672-B3D9-4C28-A346-3B2B86605010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-13875" yWindow="-21720" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="120" yWindow="24" windowWidth="23016" windowHeight="12216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="12" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -203,6 +203,21 @@
   </si>
   <si>
     <t>возможность администрирования kubernetes</t>
+  </si>
+  <si>
+    <t>https://getartcraft.com/apps/wordcraft</t>
+  </si>
+  <si>
+    <t>https://www.playground.ru/misc/news/avtor_besplatnyh_analogov_adobe_natselilsya_na_microsoft_office_razrabotchik_vypustil_pervye_versii_word_i_excel-1881260</t>
+  </si>
+  <si>
+    <t>https://kodacode.ru/</t>
+  </si>
+  <si>
+    <t>модели без vpn</t>
+  </si>
+  <si>
+    <t>Аналоги офисных программ</t>
   </si>
 </sst>
 </file>
@@ -818,7 +833,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:V30"/>
+  <dimension ref="A2:V32"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -985,7 +1000,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>28</v>
       </c>
@@ -993,7 +1008,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
         <v>30</v>
       </c>
@@ -1001,7 +1016,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>32</v>
       </c>
@@ -1009,7 +1024,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>35</v>
       </c>
@@ -1017,7 +1032,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>36</v>
       </c>
@@ -1025,7 +1040,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A22" s="23" t="s">
         <v>38</v>
       </c>
@@ -1033,7 +1048,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>41</v>
       </c>
@@ -1041,7 +1056,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>42</v>
       </c>
@@ -1049,7 +1064,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="26" t="s">
         <v>45</v>
       </c>
@@ -1057,7 +1072,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="26" t="s">
         <v>47</v>
       </c>
@@ -1068,7 +1083,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="26" t="s">
         <v>50</v>
       </c>
@@ -1076,7 +1091,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>53</v>
       </c>
@@ -1084,7 +1099,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>54</v>
       </c>
@@ -1092,12 +1107,31 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>55</v>
       </c>
       <c r="C30" s="31" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" s="26" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1108,8 +1142,11 @@
     <hyperlink ref="A25" r:id="rId3" xr:uid="{61EBBDB6-449F-431B-AC83-3C57763031B0}"/>
     <hyperlink ref="A26" r:id="rId4" location="/login" xr:uid="{B46E902B-C529-4206-BD22-BEEA9822369B}"/>
     <hyperlink ref="A27" r:id="rId5" xr:uid="{D6D2D2A3-BEEF-453F-A91F-AAB01E05A8F8}"/>
+    <hyperlink ref="C31" r:id="rId6" xr:uid="{A44B5DC5-E710-4547-AFF3-3C9E80FCEDCF}"/>
+    <hyperlink ref="C32" r:id="rId7" xr:uid="{9A0F53E3-7E91-4BEB-8933-7BDD76A7809A}"/>
+    <hyperlink ref="D31" r:id="rId8" xr:uid="{D51F4151-301F-44C8-8D64-983618191FBF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId6"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId9"/>
 </worksheet>
 </file>